--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>29.8</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>31.3</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.90</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>27.1</v>
+        <v>28.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.70</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.8</v>
+        <v>28.8</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.90</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28.8</v>
+        <v>28</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.70</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="D2" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="E2" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>29.1</v>
+        <v>30.7</v>
       </c>
       <c r="D2" t="n">
-        <v>30.6</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="n">
-        <v>32.6</v>
+        <v>34.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28.2</v>
+        <v>29.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>30.7</v>
+        <v>32.9</v>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>34.4</v>
       </c>
       <c r="E2" t="n">
-        <v>34.2</v>
+        <v>36.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.4</v>
+        <v>31.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.60</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="D2" t="n">
-        <v>34.4</v>
+        <v>33.7</v>
       </c>
       <c r="E2" t="n">
-        <v>36.4</v>
+        <v>35.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.60</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="C2" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>33.1</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>35.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.80</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31.1</v>
+        <v>30.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.80</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
-        <v>33.1</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.80</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.2</v>
+        <v>31.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.80</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>33.4</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31.1</v>
+        <v>30.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.9</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
-        <v>33.4</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.5</v>
+        <v>31.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>32.4</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="E2" t="n">
-        <v>35.9</v>
+        <v>35.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="D2" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="E2" t="n">
-        <v>35.5</v>
+        <v>36.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.40</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.6</v>
+        <v>31.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.40</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="D2" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="E2" t="n">
-        <v>36.3</v>
+        <v>35.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.40</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.40</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="E2" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="D2" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="E2" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.50</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.9</v>
+        <v>30.5</v>
       </c>
       <c r="D2" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>29.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.50</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>30.5</v>
+        <v>30.1</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.7</v>
+        <v>29</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>30.1</v>
+        <v>29.5</v>
       </c>
       <c r="D2" t="n">
-        <v>31.6</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
-        <v>33.6</v>
+        <v>33</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="C2" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E2" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.60</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.50</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>29.9</v>
+        <v>30.7</v>
       </c>
       <c r="D2" t="n">
-        <v>31.4</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="n">
-        <v>33.4</v>
+        <v>34.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.60</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.50</t>
+          <t>⚠️ 非常態變動 0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="E2" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.20</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="E2" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>─ 波動不大 0.00</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>─ 波動不大 0.00</t>
+          <t>⚠️ 非常態變動 -0.20</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.20</t>
+          <t>⚠️ 非常態變動 -0.30</t>
         </is>
       </c>
     </row>
